--- a/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,72</t>
+          <t>-0,04; 3,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,82</t>
+          <t>0,06; 3,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,96</t>
+          <t>0,04; 3,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,53</t>
+          <t>-2,23; 2,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 10,09</t>
+          <t>4,08; 9,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,66</t>
+          <t>-3,4; 0,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,46</t>
+          <t>-0,48; 2,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,23</t>
+          <t>2,8; 6,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,73</t>
+          <t>-1,03; 1,65</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 300,0</t>
+          <t>-11,78; 236,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 292,77</t>
+          <t>-3,11; 276,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 314,01</t>
+          <t>-3,18; 268,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 70,58</t>
+          <t>-37,88; 61,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,16; 287,49</t>
+          <t>64,96; 255,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,27; 17,65</t>
+          <t>-57,06; 20,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 86,14</t>
+          <t>-12,09; 83,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,17; 218,93</t>
+          <t>67,53; 233,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 64,23</t>
+          <t>-25,91; 58,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,62</t>
+          <t>-2,28; 0,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,9</t>
+          <t>-0,59; 2,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,78</t>
+          <t>-2,47; 0,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,59</t>
+          <t>-1,52; 2,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,07</t>
+          <t>2,24; 6,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,26</t>
+          <t>-1,3; 2,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,29</t>
+          <t>-1,3; 1,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,37</t>
+          <t>1,47; 4,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,97</t>
+          <t>-1,87; 1,02</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,57; 31,01</t>
+          <t>-58,28; 26,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 129,54</t>
+          <t>-14,44; 116,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 34,77</t>
+          <t>-64,68; 34,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 69,76</t>
+          <t>-25,85; 69,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,16; 185,76</t>
+          <t>38,87; 191,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 65,38</t>
+          <t>-23,32; 59,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 42,96</t>
+          <t>-29,98; 40,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,95; 136,8</t>
+          <t>32,07; 136,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 29,04</t>
+          <t>-42,36; 30,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,56</t>
+          <t>-3,37; 0,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,85</t>
+          <t>-1,09; 2,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,87</t>
+          <t>-2,24; 1,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,85</t>
+          <t>-2,12; 2,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,28</t>
+          <t>2,9; 8,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 53,42</t>
+          <t>-0,73; 57,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,7</t>
+          <t>-2,0; 0,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,95</t>
+          <t>1,44; 4,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 38,76</t>
+          <t>-0,39; 38,67</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 24,31</t>
+          <t>-69,24; 24,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 106,28</t>
+          <t>-25,88; 108,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,97; 70,25</t>
+          <t>-47,87; 63,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,81; 52,65</t>
+          <t>-35,43; 55,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,5; 223,78</t>
+          <t>48,3; 221,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 1508,05</t>
+          <t>-14,28; 1516,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,72; 19,39</t>
+          <t>-40,86; 23,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,0; 141,57</t>
+          <t>29,07; 139,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 1229,39</t>
+          <t>-9,82; 1100,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,56</t>
+          <t>0,05; 3,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,94</t>
+          <t>1,36; 5,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,35</t>
+          <t>-0,12; 3,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,39</t>
+          <t>-1,16; 2,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 11,01</t>
+          <t>5,92; 11,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,55</t>
+          <t>-1,65; 1,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,53</t>
+          <t>-0,2; 2,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,49</t>
+          <t>4,43; 7,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,99</t>
+          <t>-0,47; 2,01</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 189,12</t>
+          <t>-0,92; 185,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,0; 268,99</t>
+          <t>41,71; 274,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 183,03</t>
+          <t>-5,49; 179,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 68,32</t>
+          <t>-25,43; 76,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>108,94; 307,66</t>
+          <t>110,61; 327,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 44,39</t>
+          <t>-31,67; 46,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 87,6</t>
+          <t>-5,54; 84,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>105,55; 266,87</t>
+          <t>112,52; 271,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 69,88</t>
+          <t>-11,37; 71,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,11</t>
+          <t>-0,5; 1,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,69</t>
+          <t>0,8; 2,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,51</t>
+          <t>-0,56; 1,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,41</t>
+          <t>-0,68; 1,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,8</t>
+          <t>5,09; 7,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 22,37</t>
+          <t>-0,33; 21,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,97</t>
+          <t>-0,32; 0,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,94</t>
+          <t>3,36; 4,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 12,78</t>
+          <t>-0,0; 12,06</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 46,48</t>
+          <t>-15,98; 49,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24,92; 113,86</t>
+          <t>22,82; 103,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 63,21</t>
+          <t>-17,99; 53,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 34,39</t>
+          <t>-12,99; 35,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>100,0; 189,91</t>
+          <t>100,08; 191,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 516,71</t>
+          <t>-7,25; 471,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 27,58</t>
+          <t>-8,14; 28,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>79,92; 143,89</t>
+          <t>84,56; 148,08</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 356,2</t>
+          <t>-0,42; 331,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,57</t>
+          <t>0,09; 3,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,82</t>
+          <t>0,34; 3,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,92</t>
+          <t>0,26; 4,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,27</t>
+          <t>-2,11; 2,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 9,94</t>
+          <t>4,28; 10,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,78</t>
+          <t>-3,01; 1,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,27</t>
+          <t>-0,57; 2,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,3</t>
+          <t>2,76; 6,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,65</t>
+          <t>-0,58; 2,23</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>106,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-22,77%</t>
+          <t>-17,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 236,15</t>
+          <t>-1,57; 278,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 276,87</t>
+          <t>3,34; 290,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 268,76</t>
+          <t>2,05; 324,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 61,74</t>
+          <t>-36,52; 61,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,96; 255,76</t>
+          <t>71,94; 271,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,06; 20,75</t>
+          <t>-49,36; 33,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 83,37</t>
+          <t>-14,23; 92,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>67,53; 233,32</t>
+          <t>66,31; 230,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 58,8</t>
+          <t>-15,8; 83,71</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,53</t>
+          <t>-2,37; 0,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,58</t>
+          <t>-0,62; 2,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,83</t>
+          <t>-1,86; 1,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,58</t>
+          <t>-1,39; 2,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,79</t>
+          <t>2,29; 6,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,12</t>
+          <t>-1,37; 2,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,24</t>
+          <t>-1,39; 1,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,3</t>
+          <t>1,42; 4,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,02</t>
+          <t>-1,24; 1,25</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-25,96%</t>
+          <t>-10,87%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-8,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 26,4</t>
+          <t>-59,0; 25,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 116,87</t>
+          <t>-16,45; 136,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,68; 34,95</t>
+          <t>-49,94; 58,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 69,74</t>
+          <t>-24,41; 77,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,87; 191,9</t>
+          <t>39,63; 198,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 59,88</t>
+          <t>-23,62; 61,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 40,14</t>
+          <t>-30,56; 32,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,07; 136,25</t>
+          <t>29,57; 131,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,36; 30,83</t>
+          <t>-26,09; 39,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,97</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,96</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,44</t>
+          <t>-3,1; 0,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,84</t>
+          <t>-1,38; 2,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,64</t>
+          <t>-1,96; 1,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,06</t>
+          <t>-2,22; 2,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,48</t>
+          <t>2,83; 8,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 57,17</t>
+          <t>-1,75; 2,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,78</t>
+          <t>-2,18; 0,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,85</t>
+          <t>1,5; 5,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 38,67</t>
+          <t>-1,38; 1,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-4,95%</t>
+          <t>-2,82%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>439,18%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>286,35%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,24; 24,72</t>
+          <t>-67,81; 21,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 108,05</t>
+          <t>-28,91; 114,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 63,96</t>
+          <t>-43,77; 70,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 55,83</t>
+          <t>-38,97; 53,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48,3; 221,89</t>
+          <t>45,37; 223,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 1516,1</t>
+          <t>-29,68; 72,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 23,41</t>
+          <t>-43,8; 23,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,07; 139,96</t>
+          <t>29,99; 140,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 1100,02</t>
+          <t>-26,87; 48,73</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,32</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,12</t>
+          <t>1,4; 5,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,44</t>
+          <t>-0,1; 3,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,49</t>
+          <t>-1,35; 2,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,92; 11,1</t>
+          <t>6,11; 11,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,56</t>
+          <t>-1,19; 2,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,38</t>
+          <t>-0,21; 2,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,5</t>
+          <t>4,38; 7,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,01</t>
+          <t>-0,28; 2,01</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 185,38</t>
+          <t>-0,72; 180,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,71; 274,47</t>
+          <t>41,84; 295,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 179,05</t>
+          <t>-6,64; 182,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 76,85</t>
+          <t>-25,61; 75,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>110,61; 327,66</t>
+          <t>107,43; 332,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 46,92</t>
+          <t>-22,94; 63,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 84,45</t>
+          <t>-5,52; 83,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>112,52; 271,63</t>
+          <t>103,44; 267,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 71,7</t>
+          <t>-7,14; 73,0</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,14</t>
+          <t>-0,53; 1,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,6</t>
+          <t>0,8; 2,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,31</t>
+          <t>-0,14; 1,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,44</t>
+          <t>-0,71; 1,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,78</t>
+          <t>5,19; 7,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 21,52</t>
+          <t>-0,79; 1,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,97</t>
+          <t>-0,32; 0,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,89</t>
+          <t>3,38; 5,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 12,06</t>
+          <t>-0,13; 1,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>113,66%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 49,47</t>
+          <t>-17,06; 48,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22,82; 103,36</t>
+          <t>23,91; 110,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 53,33</t>
+          <t>-4,84; 65,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 35,32</t>
+          <t>-14,37; 33,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>100,08; 191,11</t>
+          <t>101,58; 191,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 471,61</t>
+          <t>-14,81; 27,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 28,83</t>
+          <t>-8,16; 29,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>84,56; 148,08</t>
+          <t>84,69; 146,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 331,04</t>
+          <t>-3,83; 33,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
